--- a/xlsx/tests/templates/wordle.xlsx
+++ b/xlsx/tests/templates/wordle.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/v0.9/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838FA54B-90A8-9C42-8113-F63D7679B8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F75C4B-E2F6-8F44-9646-F597A1D9924F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="401">
   <si>
     <t>Word List</t>
   </si>
@@ -1257,6 +1257,9 @@
   </si>
   <si>
     <t>CIVIC</t>
+  </si>
+  <si>
+    <t>Inspired by the original Wordle by Josh Wardle · Play the real one at nytimes.com/games/wordle</t>
   </si>
 </sst>
 </file>
@@ -1266,9 +1269,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode=";;;"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1296,14 +1306,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="22"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Aptos Narrow"/>
@@ -1312,32 +1314,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FF666666"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1372,8 +1350,54 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0563C1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1382,18 +1406,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF121213"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF818384"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1402,83 +1420,74 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFD3D6DA"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color rgb="FFD3D6DA"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color rgb="FFD3D6DA"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFD3D6DA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF222222"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF222222"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF222222"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF222222"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1516,66 +1525,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF3A3A3C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF3A3A3C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB59F3B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF538D4E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF3A3A3C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB59F3B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF538D4E"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1937,659 +1886,502 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{759913D6-48C7-FC43-926B-06425CF792FB}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;09be6901-e717-4a99-a868-261c047ad107&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:AA39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="12" width="7.1640625" customWidth="1"/>
     <col min="13" max="13" width="7" customWidth="1"/>
     <col min="14" max="14" width="7" hidden="1" customWidth="1"/>
     <col min="15" max="17" width="7" customWidth="1"/>
     <col min="18" max="19" width="7" hidden="1" customWidth="1"/>
-    <col min="20" max="27" width="10" hidden="1"/>
+    <col min="20" max="27" width="10" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="N1" s="15" t="s">
+    <row r="1" spans="2:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N1" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-    </row>
-    <row r="2" spans="1:27" ht="41.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+    </row>
+    <row r="2" spans="2:27" ht="41.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="N2" s="16" t="str" cm="1">
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="N2" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="N2" ca="1">INDEX(_xlfn._xlws.FILTER(Words!$A$2:$A$1000,Words!$B$2:$B$1000=TRUE),MOD(TODAY()-DATE(2024,1,1),Words!$C$2)+1)</f>
-        <v>RHINO</v>
-      </c>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-    </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-    </row>
-    <row r="4" spans="1:27" ht="41.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="R4" s="8" t="str">
+        <v>BELOW</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:27" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="R4" s="3" t="str">
         <f>Engine!A3</f>
         <v/>
       </c>
-      <c r="S4" s="8" t="str">
+      <c r="S4" s="3" t="str">
         <f>Engine!B3</f>
         <v/>
       </c>
-      <c r="T4" s="9" t="str">
+      <c r="T4" s="3" t="str">
         <f>Engine!C3</f>
         <v/>
       </c>
-      <c r="U4" s="9" t="str">
+      <c r="U4" s="3" t="str">
         <f>Engine!D3</f>
         <v/>
       </c>
-      <c r="V4" s="9" t="str">
+      <c r="V4" s="3" t="str">
         <f>Engine!E3</f>
         <v/>
       </c>
-      <c r="W4" s="9" t="str">
+      <c r="W4" s="3" t="str">
         <f>Engine!G3</f>
         <v/>
       </c>
-      <c r="X4" s="9" t="str">
+      <c r="X4" s="3" t="str">
         <f>Engine!H3</f>
         <v/>
       </c>
-      <c r="Y4" s="9" t="str">
+      <c r="Y4" s="3" t="str">
         <f>Engine!I3</f>
         <v/>
       </c>
-      <c r="Z4" s="9" t="str">
+      <c r="Z4" s="3" t="str">
         <f>Engine!J3</f>
         <v/>
       </c>
-      <c r="AA4" s="9" t="str">
+      <c r="AA4" s="3" t="str">
         <f>Engine!K3</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="41.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="R5" s="8" t="str">
+    <row r="5" spans="2:27" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="R5" s="3" t="str">
         <f>Engine!A4</f>
         <v/>
       </c>
-      <c r="S5" s="8" t="str">
+      <c r="S5" s="3" t="str">
         <f>Engine!B4</f>
         <v/>
       </c>
-      <c r="T5" s="9" t="str">
+      <c r="T5" s="3" t="str">
         <f>Engine!C4</f>
         <v/>
       </c>
-      <c r="U5" s="9" t="str">
+      <c r="U5" s="3" t="str">
         <f>Engine!D4</f>
         <v/>
       </c>
-      <c r="V5" s="9" t="str">
+      <c r="V5" s="3" t="str">
         <f>Engine!E4</f>
         <v/>
       </c>
-      <c r="W5" s="9" t="str">
+      <c r="W5" s="3" t="str">
         <f>Engine!G4</f>
         <v/>
       </c>
-      <c r="X5" s="9" t="str">
+      <c r="X5" s="3" t="str">
         <f>Engine!H4</f>
         <v/>
       </c>
-      <c r="Y5" s="9" t="str">
+      <c r="Y5" s="3" t="str">
         <f>Engine!I4</f>
         <v/>
       </c>
-      <c r="Z5" s="9" t="str">
+      <c r="Z5" s="3" t="str">
         <f>Engine!J4</f>
         <v/>
       </c>
-      <c r="AA5" s="9" t="str">
+      <c r="AA5" s="3" t="str">
         <f>Engine!K4</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="41.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="R6" s="8" t="str">
+    <row r="6" spans="2:27" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="R6" s="3" t="str">
         <f>Engine!A5</f>
         <v/>
       </c>
-      <c r="S6" s="8" t="str">
+      <c r="S6" s="3" t="str">
         <f>Engine!B5</f>
         <v/>
       </c>
-      <c r="T6" s="9" t="str">
+      <c r="T6" s="3" t="str">
         <f>Engine!C5</f>
         <v/>
       </c>
-      <c r="U6" s="9" t="str">
+      <c r="U6" s="3" t="str">
         <f>Engine!D5</f>
         <v/>
       </c>
-      <c r="V6" s="9" t="str">
+      <c r="V6" s="3" t="str">
         <f>Engine!E5</f>
         <v/>
       </c>
-      <c r="W6" s="9" t="str">
+      <c r="W6" s="3" t="str">
         <f>Engine!G5</f>
         <v/>
       </c>
-      <c r="X6" s="9" t="str">
+      <c r="X6" s="3" t="str">
         <f>Engine!H5</f>
         <v/>
       </c>
-      <c r="Y6" s="9" t="str">
+      <c r="Y6" s="3" t="str">
         <f>Engine!I5</f>
         <v/>
       </c>
-      <c r="Z6" s="9" t="str">
+      <c r="Z6" s="3" t="str">
         <f>Engine!J5</f>
         <v/>
       </c>
-      <c r="AA6" s="9" t="str">
+      <c r="AA6" s="3" t="str">
         <f>Engine!K5</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="41.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="R7" s="8" t="str">
+    <row r="7" spans="2:27" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="R7" s="3" t="str">
         <f>Engine!A6</f>
         <v/>
       </c>
-      <c r="S7" s="8" t="str">
+      <c r="S7" s="3" t="str">
         <f>Engine!B6</f>
         <v/>
       </c>
-      <c r="T7" s="9" t="str">
+      <c r="T7" s="3" t="str">
         <f>Engine!C6</f>
         <v/>
       </c>
-      <c r="U7" s="9" t="str">
+      <c r="U7" s="3" t="str">
         <f>Engine!D6</f>
         <v/>
       </c>
-      <c r="V7" s="9" t="str">
+      <c r="V7" s="3" t="str">
         <f>Engine!E6</f>
         <v/>
       </c>
-      <c r="W7" s="9" t="str">
+      <c r="W7" s="3" t="str">
         <f>Engine!G6</f>
         <v/>
       </c>
-      <c r="X7" s="9" t="str">
+      <c r="X7" s="3" t="str">
         <f>Engine!H6</f>
         <v/>
       </c>
-      <c r="Y7" s="9" t="str">
+      <c r="Y7" s="3" t="str">
         <f>Engine!I6</f>
         <v/>
       </c>
-      <c r="Z7" s="9" t="str">
+      <c r="Z7" s="3" t="str">
         <f>Engine!J6</f>
         <v/>
       </c>
-      <c r="AA7" s="9" t="str">
+      <c r="AA7" s="3" t="str">
         <f>Engine!K6</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="41.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="R8" s="8" t="str">
+    <row r="8" spans="2:27" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="R8" s="3" t="str">
         <f>Engine!A7</f>
         <v/>
       </c>
-      <c r="S8" s="8" t="str">
+      <c r="S8" s="3" t="str">
         <f>Engine!B7</f>
         <v/>
       </c>
-      <c r="T8" s="9" t="str">
+      <c r="T8" s="3" t="str">
         <f>Engine!C7</f>
         <v/>
       </c>
-      <c r="U8" s="9" t="str">
+      <c r="U8" s="3" t="str">
         <f>Engine!D7</f>
         <v/>
       </c>
-      <c r="V8" s="9" t="str">
+      <c r="V8" s="3" t="str">
         <f>Engine!E7</f>
         <v/>
       </c>
-      <c r="W8" s="9" t="str">
+      <c r="W8" s="3" t="str">
         <f>Engine!G7</f>
         <v/>
       </c>
-      <c r="X8" s="9" t="str">
+      <c r="X8" s="3" t="str">
         <f>Engine!H7</f>
         <v/>
       </c>
-      <c r="Y8" s="9" t="str">
+      <c r="Y8" s="3" t="str">
         <f>Engine!I7</f>
         <v/>
       </c>
-      <c r="Z8" s="9" t="str">
+      <c r="Z8" s="3" t="str">
         <f>Engine!J7</f>
         <v/>
       </c>
-      <c r="AA8" s="9" t="str">
+      <c r="AA8" s="3" t="str">
         <f>Engine!K7</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="41.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="R9" s="8" t="str">
+    <row r="9" spans="2:27" ht="41.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="R9" s="3" t="str">
         <f>Engine!A8</f>
         <v/>
       </c>
-      <c r="S9" s="8" t="str">
+      <c r="S9" s="3" t="str">
         <f>Engine!B8</f>
         <v/>
       </c>
-      <c r="T9" s="9" t="str">
+      <c r="T9" s="3" t="str">
         <f>Engine!C8</f>
         <v/>
       </c>
-      <c r="U9" s="9" t="str">
+      <c r="U9" s="3" t="str">
         <f>Engine!D8</f>
         <v/>
       </c>
-      <c r="V9" s="9" t="str">
+      <c r="V9" s="3" t="str">
         <f>Engine!E8</f>
         <v/>
       </c>
-      <c r="W9" s="9" t="str">
+      <c r="W9" s="3" t="str">
         <f>Engine!G8</f>
         <v/>
       </c>
-      <c r="X9" s="9" t="str">
+      <c r="X9" s="3" t="str">
         <f>Engine!H8</f>
         <v/>
       </c>
-      <c r="Y9" s="9" t="str">
+      <c r="Y9" s="3" t="str">
         <f>Engine!I8</f>
         <v/>
       </c>
-      <c r="Z9" s="9" t="str">
+      <c r="Z9" s="3" t="str">
         <f>Engine!J8</f>
         <v/>
       </c>
-      <c r="AA9" s="9" t="str">
+      <c r="AA9" s="3" t="str">
         <f>Engine!K8</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="11.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-    </row>
-    <row r="11" spans="1:27" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6" t="str">
+    <row r="10" spans="2:27" ht="11.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="2:27" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="11"/>
+      <c r="D11" s="17" t="str">
         <f>IF(OR(COUNTIF(R4:V4,TRUE)=5,COUNTIF(R5:V5,TRUE)=5,COUNTIF(R6:V6,TRUE)=5,COUNTIF(R7:V7,TRUE)=5,COUNTIF(R8:V8,TRUE)=5,COUNTIF(R9:V9,TRUE)=5),"🎉 Correct! Well done!",IF(AND(NOT(OR(COUNTIF(R4:V4,TRUE)=5,COUNTIF(R5:V5,TRUE)=5,COUNTIF(R6:V6,TRUE)=5,COUNTIF(R7:V7,TRUE)=5,COUNTIF(R8:V8,TRUE)=5,COUNTIF(R9:V9,TRUE)=5)),D9&lt;&gt;""),"Game over — the word was "&amp;UPPER($N$2),"Guess "&amp;COUNTA(D4:D9)+1&amp;" of 6"))</f>
         <v>Guess 1 of 6</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" ht="11.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-    </row>
-    <row r="13" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
-      <c r="B13" s="7" t="s">
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+    </row>
+    <row r="12" spans="2:27" ht="11.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="L13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-    </row>
-    <row r="14" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="7" t="s">
+    </row>
+    <row r="14" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="7" t="s">
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" spans="2:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="15"/>
+      <c r="C15" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-    </row>
-    <row r="16" spans="1:27" ht="11.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="1:19" ht="11.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="17"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+    </row>
+    <row r="16" spans="2:27" ht="11.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="2:12" ht="11.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="18" t="s">
+        <v>127</v>
+      </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
-      <c r="F17" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-    </row>
-    <row r="18" spans="1:19" ht="11.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="17"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+    </row>
+    <row r="18" spans="2:12" ht="11.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="18" t="s">
+        <v>128</v>
+      </c>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
-      <c r="F18" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="1:19" ht="11.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="1:19" ht="11.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+    </row>
+    <row r="19" spans="2:12" ht="11.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+    </row>
+    <row r="20" spans="2:12" ht="11.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2598,41 +2390,22 @@
     <row r="38" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="39" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
+  <mergeCells count="5">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="B19:J19"/>
   </mergeCells>
-  <conditionalFormatting sqref="B14:J14">
-    <cfRule type="expression" dxfId="12" priority="34">
-      <formula>AND(B14&lt;&gt;"",SUMPRODUCT((UPPER($D$4:$H$9)=UPPER(B14))*(MID(UPPER($N$2),COLUMN($D$4:$H$9)-COLUMN($D$4)+1,1)=UPPER(B14)))&gt;0)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="35">
-      <formula>AND(B14&lt;&gt;"",COUNTIF($D$4:$H$9,B14)&gt;0,ISNUMBER(FIND(UPPER(B14),UPPER($N$2))))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="36">
-      <formula>AND(B14&lt;&gt;"",COUNTIF($D$4:$H$9,B14)&gt;0,ISNUMBER(FIND(UPPER(B14),UPPER($N$2)))=FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13:K13">
-    <cfRule type="expression" dxfId="9" priority="4">
+  <conditionalFormatting sqref="B13:K13 B14:J14 C15:I15">
+    <cfRule type="expression" dxfId="6" priority="34">
       <formula>AND(B13&lt;&gt;"",SUMPRODUCT((UPPER($D$4:$H$9)=UPPER(B13))*(MID(UPPER($N$2),COLUMN($D$4:$H$9)-COLUMN($D$4)+1,1)=UPPER(B13)))&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="5">
+    <cfRule type="expression" dxfId="5" priority="35">
       <formula>AND(B13&lt;&gt;"",COUNTIF($D$4:$H$9,B13)&gt;0,ISNUMBER(FIND(UPPER(B13),UPPER($N$2))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="6">
+    <cfRule type="expression" dxfId="4" priority="36">
       <formula>AND(B13&lt;&gt;"",COUNTIF($D$4:$H$9,B13)&gt;0,ISNUMBER(FIND(UPPER(B13),UPPER($N$2)))=FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C15:I15">
-    <cfRule type="expression" dxfId="6" priority="61">
-      <formula>AND(C15&lt;&gt;"",SUMPRODUCT((UPPER($D$4:$H$9)=UPPER(C15))*(MID(UPPER($N$2),COLUMN($D$4:$H$9)-COLUMN($D$4)+1,1)=UPPER(C15)))&gt;0)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="62">
-      <formula>AND(C15&lt;&gt;"",COUNTIF($D$4:$H$9,C15)&gt;0,ISNUMBER(FIND(UPPER(C15),UPPER($N$2))))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="63">
-      <formula>AND(C15&lt;&gt;"",COUNTIF($D$4:$H$9,C15)&gt;0,ISNUMBER(FIND(UPPER(C15),UPPER($N$2)))=FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:H9">
@@ -2646,6 +2419,9 @@
       <formula>R4=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="B19" r:id="rId1" tooltip="Play the real Wordle (New York Times)" xr:uid="{6103356C-A9E3-694C-B8CB-1BBF54D3654C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2653,27 +2429,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D1000"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2681,12 +2457,12 @@
         <f t="shared" ref="B2:B65" si="0">IF(A2="","",_xlfn.REGEXTEST(A2,"^[A-Z]{5}$"))</f>
         <v>1</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="7">
         <f>COUNTIF(B2:B1000,TRUE)</f>
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2695,7 +2471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2704,7 +2480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2713,7 +2489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -2722,7 +2498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -2731,7 +2507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -2740,7 +2516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -2749,7 +2525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -2758,7 +2534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2767,7 +2543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -2776,7 +2552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -2785,7 +2561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -2794,7 +2570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -2803,7 +2579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -2812,7 +2588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -2821,7 +2597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -2830,7 +2606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -2839,7 +2615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -2848,7 +2624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -2857,7 +2633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -2866,7 +2642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
@@ -2875,7 +2651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
@@ -2884,7 +2660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -2893,7 +2669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
@@ -2902,7 +2678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
@@ -2911,7 +2687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
@@ -2920,7 +2696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
@@ -2929,7 +2705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
@@ -2938,7 +2714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
@@ -2947,7 +2723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
@@ -2956,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
@@ -2965,7 +2741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
@@ -2974,7 +2750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
@@ -2983,7 +2759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
@@ -2992,7 +2768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
@@ -3001,7 +2777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
@@ -3010,7 +2786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
@@ -3019,7 +2795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>39</v>
       </c>
@@ -3028,7 +2804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>40</v>
       </c>
@@ -3037,7 +2813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>41</v>
       </c>
@@ -3046,7 +2822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>42</v>
       </c>
@@ -3055,7 +2831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
@@ -3064,7 +2840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
@@ -3073,7 +2849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>45</v>
       </c>
@@ -3082,7 +2858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>46</v>
       </c>
@@ -3091,7 +2867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
@@ -3100,7 +2876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>48</v>
       </c>
@@ -3109,7 +2885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>49</v>
       </c>
@@ -3118,7 +2894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>50</v>
       </c>
@@ -3127,7 +2903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>51</v>
       </c>
@@ -3136,7 +2912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>52</v>
       </c>
@@ -3145,7 +2921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>53</v>
       </c>
@@ -3154,7 +2930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>54</v>
       </c>
@@ -3163,7 +2939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>55</v>
       </c>
@@ -3172,7 +2948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>56</v>
       </c>
@@ -3181,7 +2957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>57</v>
       </c>
@@ -3190,7 +2966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>58</v>
       </c>
@@ -3199,7 +2975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>59</v>
       </c>
@@ -3208,7 +2984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>60</v>
       </c>
@@ -3217,7 +2993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>61</v>
       </c>
@@ -3226,7 +3002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>62</v>
       </c>
@@ -3235,7 +3011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>63</v>
       </c>
@@ -3244,7 +3020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>64</v>
       </c>
@@ -3253,7 +3029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>65</v>
       </c>
@@ -3262,7 +3038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>66</v>
       </c>
@@ -3271,7 +3047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>67</v>
       </c>
@@ -3280,7 +3056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>68</v>
       </c>
@@ -3289,7 +3065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>69</v>
       </c>
@@ -3298,7 +3074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>70</v>
       </c>
@@ -3307,7 +3083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>71</v>
       </c>
@@ -3316,7 +3092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>72</v>
       </c>
@@ -3325,7 +3101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>73</v>
       </c>
@@ -3334,7 +3110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>74</v>
       </c>
@@ -3343,7 +3119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>75</v>
       </c>
@@ -3352,7 +3128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>76</v>
       </c>
@@ -3361,7 +3137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>77</v>
       </c>
@@ -3370,7 +3146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>78</v>
       </c>
@@ -3379,7 +3155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>79</v>
       </c>
@@ -3388,7 +3164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>80</v>
       </c>
@@ -3397,7 +3173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>81</v>
       </c>
@@ -3406,7 +3182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>82</v>
       </c>
@@ -3415,7 +3191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>83</v>
       </c>
@@ -3424,7 +3200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>84</v>
       </c>
@@ -3433,7 +3209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>85</v>
       </c>
@@ -3442,7 +3218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>86</v>
       </c>
@@ -3451,7 +3227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>87</v>
       </c>
@@ -3460,7 +3236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>88</v>
       </c>
@@ -3469,7 +3245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>89</v>
       </c>
@@ -3478,7 +3254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>90</v>
       </c>
@@ -3487,7 +3263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>91</v>
       </c>
@@ -3496,7 +3272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>92</v>
       </c>
@@ -3505,7 +3281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>93</v>
       </c>
@@ -3514,7 +3290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>94</v>
       </c>
@@ -3523,7 +3299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>95</v>
       </c>
@@ -3532,7 +3308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>96</v>
       </c>
@@ -3541,7 +3317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>97</v>
       </c>
@@ -3550,7 +3326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>98</v>
       </c>
@@ -3559,7 +3335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>133</v>
       </c>
@@ -3568,7 +3344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>134</v>
       </c>
@@ -3577,7 +3353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>135</v>
       </c>
@@ -3586,7 +3362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>136</v>
       </c>
@@ -3595,7 +3371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>137</v>
       </c>
@@ -3604,7 +3380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>138</v>
       </c>
@@ -3613,7 +3389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>139</v>
       </c>
@@ -3622,7 +3398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>140</v>
       </c>
@@ -3631,7 +3407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>141</v>
       </c>
@@ -3640,7 +3416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>142</v>
       </c>
@@ -3649,7 +3425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>143</v>
       </c>
@@ -3658,7 +3434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>144</v>
       </c>
@@ -3667,7 +3443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>145</v>
       </c>
@@ -3676,7 +3452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>146</v>
       </c>
@@ -3685,7 +3461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>147</v>
       </c>
@@ -3694,7 +3470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>148</v>
       </c>
@@ -3703,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>149</v>
       </c>
@@ -3712,7 +3488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>150</v>
       </c>
@@ -3721,7 +3497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>151</v>
       </c>
@@ -3730,7 +3506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>152</v>
       </c>
@@ -3739,7 +3515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>153</v>
       </c>
@@ -3748,7 +3524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>154</v>
       </c>
@@ -3757,7 +3533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>155</v>
       </c>
@@ -3766,7 +3542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>156</v>
       </c>
@@ -3775,7 +3551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>157</v>
       </c>
@@ -3784,7 +3560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>158</v>
       </c>
@@ -3793,7 +3569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>159</v>
       </c>
@@ -3802,7 +3578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>160</v>
       </c>
@@ -3811,7 +3587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>161</v>
       </c>
@@ -3820,7 +3596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>162</v>
       </c>
@@ -3829,7 +3605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>163</v>
       </c>
@@ -3838,7 +3614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>164</v>
       </c>
@@ -3847,7 +3623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>165</v>
       </c>
@@ -3856,7 +3632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>166</v>
       </c>
@@ -3865,7 +3641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>167</v>
       </c>
@@ -3874,7 +3650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>168</v>
       </c>
@@ -3883,7 +3659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>169</v>
       </c>
@@ -3892,7 +3668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>170</v>
       </c>
@@ -3901,7 +3677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>171</v>
       </c>
@@ -3910,7 +3686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>172</v>
       </c>
@@ -3919,7 +3695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>173</v>
       </c>
@@ -3928,7 +3704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>174</v>
       </c>
@@ -3937,7 +3713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>175</v>
       </c>
@@ -3946,7 +3722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>176</v>
       </c>
@@ -3955,7 +3731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>177</v>
       </c>
@@ -3964,7 +3740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>178</v>
       </c>
@@ -3973,7 +3749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>179</v>
       </c>
@@ -3982,7 +3758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>180</v>
       </c>
@@ -3991,7 +3767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>181</v>
       </c>
@@ -4000,7 +3776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>182</v>
       </c>
@@ -4009,7 +3785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>183</v>
       </c>
@@ -4018,7 +3794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>184</v>
       </c>
@@ -4027,7 +3803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>185</v>
       </c>
@@ -4036,7 +3812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>186</v>
       </c>
@@ -4045,7 +3821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>187</v>
       </c>
@@ -4054,7 +3830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>188</v>
       </c>
@@ -4063,7 +3839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>189</v>
       </c>
@@ -4072,7 +3848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>190</v>
       </c>
@@ -4081,7 +3857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>191</v>
       </c>
@@ -4090,7 +3866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>192</v>
       </c>
@@ -4099,7 +3875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>193</v>
       </c>
@@ -4108,7 +3884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>194</v>
       </c>
@@ -4117,7 +3893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>195</v>
       </c>
@@ -4126,7 +3902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>196</v>
       </c>
@@ -4135,7 +3911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>197</v>
       </c>
@@ -4144,7 +3920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>198</v>
       </c>
@@ -4153,7 +3929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -4162,7 +3938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>200</v>
       </c>
@@ -4171,7 +3947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>201</v>
       </c>
@@ -4180,7 +3956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>202</v>
       </c>
@@ -4189,7 +3965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>203</v>
       </c>
@@ -4198,7 +3974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>204</v>
       </c>
@@ -4207,7 +3983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>205</v>
       </c>
@@ -4216,7 +3992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>206</v>
       </c>
@@ -4225,7 +4001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>207</v>
       </c>
@@ -4234,7 +4010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>208</v>
       </c>
@@ -4243,7 +4019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>209</v>
       </c>
@@ -4252,7 +4028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>210</v>
       </c>
@@ -4261,7 +4037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>211</v>
       </c>
@@ -4270,7 +4046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>212</v>
       </c>
@@ -4279,7 +4055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>213</v>
       </c>
@@ -4288,7 +4064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>214</v>
       </c>
@@ -4297,7 +4073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>215</v>
       </c>
@@ -4306,7 +4082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>216</v>
       </c>
@@ -4315,7 +4091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>217</v>
       </c>
@@ -4324,7 +4100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>218</v>
       </c>
@@ -4333,7 +4109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>219</v>
       </c>
@@ -4342,7 +4118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>220</v>
       </c>
@@ -4351,7 +4127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>221</v>
       </c>
@@ -4360,7 +4136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>222</v>
       </c>
@@ -4369,7 +4145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>223</v>
       </c>
@@ -4378,7 +4154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>224</v>
       </c>
@@ -4387,7 +4163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>225</v>
       </c>
@@ -4396,7 +4172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>226</v>
       </c>
@@ -4405,7 +4181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>227</v>
       </c>
@@ -4414,7 +4190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>228</v>
       </c>
@@ -4423,7 +4199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>229</v>
       </c>
@@ -4432,7 +4208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>230</v>
       </c>
@@ -4441,7 +4217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>231</v>
       </c>
@@ -4450,7 +4226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>232</v>
       </c>
@@ -4459,7 +4235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>233</v>
       </c>
@@ -4468,7 +4244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>234</v>
       </c>
@@ -4477,7 +4253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>235</v>
       </c>
@@ -4486,7 +4262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>236</v>
       </c>
@@ -4495,7 +4271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>237</v>
       </c>
@@ -4504,7 +4280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>238</v>
       </c>
@@ -4513,7 +4289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>239</v>
       </c>
@@ -4522,7 +4298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>240</v>
       </c>
@@ -4531,7 +4307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>241</v>
       </c>
@@ -4540,7 +4316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>242</v>
       </c>
@@ -4549,7 +4325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>243</v>
       </c>
@@ -4558,7 +4334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>244</v>
       </c>
@@ -4567,7 +4343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>245</v>
       </c>
@@ -4576,7 +4352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>246</v>
       </c>
@@ -4585,7 +4361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>247</v>
       </c>
@@ -4594,7 +4370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>248</v>
       </c>
@@ -4603,7 +4379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>249</v>
       </c>
@@ -4612,7 +4388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>250</v>
       </c>
@@ -4621,7 +4397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>251</v>
       </c>
@@ -4630,7 +4406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>252</v>
       </c>
@@ -4639,7 +4415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>253</v>
       </c>
@@ -4648,7 +4424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>254</v>
       </c>
@@ -4657,7 +4433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>255</v>
       </c>
@@ -4666,7 +4442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>256</v>
       </c>
@@ -4675,7 +4451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>257</v>
       </c>
@@ -4684,7 +4460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>258</v>
       </c>
@@ -4693,7 +4469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>259</v>
       </c>
@@ -4702,7 +4478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>260</v>
       </c>
@@ -4711,7 +4487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>261</v>
       </c>
@@ -4720,7 +4496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>262</v>
       </c>
@@ -4729,7 +4505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>263</v>
       </c>
@@ -4738,7 +4514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>264</v>
       </c>
@@ -4747,7 +4523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>265</v>
       </c>
@@ -4756,7 +4532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>266</v>
       </c>
@@ -4765,7 +4541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>267</v>
       </c>
@@ -4774,7 +4550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>268</v>
       </c>
@@ -4783,7 +4559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>269</v>
       </c>
@@ -4792,7 +4568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>270</v>
       </c>
@@ -4801,7 +4577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>271</v>
       </c>
@@ -4810,7 +4586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>272</v>
       </c>
@@ -4819,7 +4595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>273</v>
       </c>
@@ -4828,7 +4604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>274</v>
       </c>
@@ -4837,7 +4613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>275</v>
       </c>
@@ -4846,7 +4622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>276</v>
       </c>
@@ -4855,7 +4631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>277</v>
       </c>
@@ -4864,7 +4640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>278</v>
       </c>
@@ -4873,7 +4649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>279</v>
       </c>
@@ -4882,7 +4658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>280</v>
       </c>
@@ -4891,7 +4667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>281</v>
       </c>
@@ -4900,7 +4676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>282</v>
       </c>
@@ -4909,7 +4685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>283</v>
       </c>
@@ -4918,7 +4694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>284</v>
       </c>
@@ -4927,7 +4703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>285</v>
       </c>
@@ -4936,7 +4712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>286</v>
       </c>
@@ -4945,7 +4721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>287</v>
       </c>
@@ -4954,7 +4730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>288</v>
       </c>
@@ -4963,7 +4739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>289</v>
       </c>
@@ -4972,7 +4748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>290</v>
       </c>
@@ -4981,7 +4757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>291</v>
       </c>
@@ -4990,7 +4766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>292</v>
       </c>
@@ -4999,7 +4775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>293</v>
       </c>
@@ -5008,7 +4784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>294</v>
       </c>
@@ -5017,7 +4793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>295</v>
       </c>
@@ -5026,7 +4802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>296</v>
       </c>
@@ -5035,7 +4811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>297</v>
       </c>
@@ -5044,7 +4820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>298</v>
       </c>
@@ -5053,7 +4829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>299</v>
       </c>
@@ -5062,7 +4838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>300</v>
       </c>
@@ -5071,7 +4847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>301</v>
       </c>
@@ -5080,7 +4856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>302</v>
       </c>
@@ -5089,7 +4865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>303</v>
       </c>
@@ -5098,7 +4874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>304</v>
       </c>
@@ -5107,7 +4883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>305</v>
       </c>
@@ -5116,7 +4892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>306</v>
       </c>
@@ -5125,7 +4901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>307</v>
       </c>
@@ -5134,7 +4910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>308</v>
       </c>
@@ -5143,7 +4919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>309</v>
       </c>
@@ -5152,7 +4928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>310</v>
       </c>
@@ -5161,7 +4937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>311</v>
       </c>
@@ -5170,7 +4946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>312</v>
       </c>
@@ -5179,7 +4955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>313</v>
       </c>
@@ -5188,7 +4964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>314</v>
       </c>
@@ -5197,7 +4973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>315</v>
       </c>
@@ -5206,7 +4982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>316</v>
       </c>
@@ -5215,7 +4991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>317</v>
       </c>
@@ -5224,7 +5000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>318</v>
       </c>
@@ -5233,7 +5009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>319</v>
       </c>
@@ -5242,7 +5018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>320</v>
       </c>
@@ -5251,7 +5027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>321</v>
       </c>
@@ -5260,7 +5036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>322</v>
       </c>
@@ -5269,7 +5045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>323</v>
       </c>
@@ -5278,7 +5054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>324</v>
       </c>
@@ -5287,7 +5063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>325</v>
       </c>
@@ -5296,7 +5072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>326</v>
       </c>
@@ -5305,7 +5081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>327</v>
       </c>
@@ -5314,7 +5090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>328</v>
       </c>
@@ -5323,7 +5099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>329</v>
       </c>
@@ -5332,7 +5108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>330</v>
       </c>
@@ -5341,7 +5117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>331</v>
       </c>
@@ -5350,7 +5126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>332</v>
       </c>
@@ -5359,7 +5135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>333</v>
       </c>
@@ -5368,7 +5144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>334</v>
       </c>
@@ -5377,7 +5153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>335</v>
       </c>
@@ -5386,7 +5162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>336</v>
       </c>
@@ -5395,7 +5171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>337</v>
       </c>
@@ -5404,7 +5180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>338</v>
       </c>
@@ -5413,7 +5189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>339</v>
       </c>
@@ -5422,7 +5198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>340</v>
       </c>
@@ -5431,7 +5207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>341</v>
       </c>
@@ -5440,7 +5216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>342</v>
       </c>
@@ -5449,7 +5225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>343</v>
       </c>
@@ -5458,7 +5234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>344</v>
       </c>
@@ -5467,7 +5243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>345</v>
       </c>
@@ -5476,7 +5252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>346</v>
       </c>
@@ -5485,7 +5261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>347</v>
       </c>
@@ -5494,7 +5270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>348</v>
       </c>
@@ -5503,7 +5279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>349</v>
       </c>
@@ -5512,7 +5288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>350</v>
       </c>
@@ -5521,7 +5297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>351</v>
       </c>
@@ -5530,7 +5306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>352</v>
       </c>
@@ -5539,7 +5315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>353</v>
       </c>
@@ -5548,7 +5324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>354</v>
       </c>
@@ -5557,7 +5333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>355</v>
       </c>
@@ -5566,7 +5342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>356</v>
       </c>
@@ -5575,7 +5351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>357</v>
       </c>
@@ -5584,7 +5360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>358</v>
       </c>
@@ -5593,7 +5369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>359</v>
       </c>
@@ -5602,7 +5378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>360</v>
       </c>
@@ -5611,7 +5387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>361</v>
       </c>
@@ -5620,7 +5396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>362</v>
       </c>
@@ -5629,7 +5405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>363</v>
       </c>
@@ -5638,7 +5414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>364</v>
       </c>
@@ -5647,7 +5423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>365</v>
       </c>
@@ -5656,7 +5432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>366</v>
       </c>
@@ -5665,7 +5441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>367</v>
       </c>
@@ -5674,7 +5450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>368</v>
       </c>
@@ -5683,7 +5459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>369</v>
       </c>
@@ -5692,7 +5468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>370</v>
       </c>
@@ -5701,7 +5477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>371</v>
       </c>
@@ -5710,7 +5486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>372</v>
       </c>
@@ -5719,7 +5495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>373</v>
       </c>
@@ -5728,7 +5504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>374</v>
       </c>
@@ -5737,7 +5513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>375</v>
       </c>
@@ -5746,7 +5522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>376</v>
       </c>
@@ -5755,7 +5531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>377</v>
       </c>
@@ -5764,7 +5540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>378</v>
       </c>
@@ -5773,7 +5549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>379</v>
       </c>
@@ -5782,7 +5558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>380</v>
       </c>
@@ -5791,7 +5567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>381</v>
       </c>
@@ -5800,7 +5576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>382</v>
       </c>
@@ -5809,7 +5585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>383</v>
       </c>
@@ -5818,7 +5594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>384</v>
       </c>
@@ -5827,7 +5603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>385</v>
       </c>
@@ -5836,7 +5612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>386</v>
       </c>
@@ -5845,7 +5621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>387</v>
       </c>
@@ -5854,7 +5630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>388</v>
       </c>
@@ -5863,7 +5639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>389</v>
       </c>
@@ -5872,7 +5648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>390</v>
       </c>
@@ -5881,7 +5657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>391</v>
       </c>
@@ -5890,7 +5666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>392</v>
       </c>
@@ -5899,7 +5675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>393</v>
       </c>
@@ -5908,7 +5684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>394</v>
       </c>
@@ -5917,7 +5693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>395</v>
       </c>
@@ -5926,7 +5702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>396</v>
       </c>
@@ -5935,7 +5711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>397</v>
       </c>
@@ -5944,7 +5720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>398</v>
       </c>
@@ -5953,7 +5729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>399</v>
       </c>
@@ -5962,2788 +5738,2788 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B367" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="368" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B368" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="369" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="369" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B369" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="370" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="370" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B370" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="371" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="371" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B371" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="372" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="372" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B372" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="373" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="373" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B373" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="374" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="374" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B374" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="375" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="375" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B375" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="376" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="376" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B376" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="377" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="377" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B377" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="378" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="378" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B378" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="379" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="379" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B379" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="380" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="380" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B380" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="381" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="381" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B381" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="382" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="382" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B382" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="383" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="383" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B383" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="384" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="384" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B384" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="385" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="385" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B385" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="386" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="386" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B386" s="2" t="str">
         <f t="shared" ref="B386:B449" si="6">IF(A386="","",_xlfn.REGEXTEST(A386,"^[A-Z]{5}$"))</f>
         <v/>
       </c>
     </row>
-    <row r="387" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="387" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B387" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="388" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="388" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B388" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="389" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="389" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B389" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="390" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="390" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B390" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="391" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="391" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B391" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="392" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="392" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B392" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="393" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="393" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B393" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="394" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="394" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B394" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="395" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="395" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B395" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="396" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="396" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B396" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="397" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="397" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B397" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="398" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="398" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B398" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="399" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="399" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B399" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="400" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="400" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B400" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="401" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="401" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B401" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="402" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="402" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B402" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="403" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="403" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B403" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="404" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="404" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B404" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="405" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="405" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B405" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="406" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="406" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B406" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="407" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="407" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B407" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="408" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="408" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B408" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="409" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="409" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B409" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="410" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="410" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B410" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="411" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="411" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B411" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="412" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="412" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B412" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="413" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="413" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B413" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="414" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="414" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B414" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="415" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="415" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B415" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="416" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="416" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B416" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="417" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="417" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B417" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="418" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="418" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B418" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="419" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="419" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B419" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="420" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="420" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B420" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="421" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="421" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B421" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="422" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="422" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B422" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="423" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="423" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B423" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="424" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="424" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B424" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="425" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="425" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B425" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="426" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="426" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B426" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="427" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="427" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B427" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="428" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="428" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B428" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="429" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="429" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B429" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="430" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="430" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B430" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="431" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="431" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B431" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="432" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="432" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B432" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="433" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="433" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B433" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="434" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="434" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B434" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="435" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="435" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B435" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="436" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="436" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B436" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="437" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="437" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B437" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="438" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="438" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B438" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="439" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="439" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B439" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="440" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="440" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B440" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="441" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="441" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B441" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="442" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="442" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B442" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="443" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="443" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B443" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="444" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="444" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B444" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="445" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="445" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B445" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="446" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="446" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B446" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="447" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="447" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B447" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="448" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="448" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B448" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="449" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="449" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B449" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="450" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="450" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B450" s="2" t="str">
         <f t="shared" ref="B450:B513" si="7">IF(A450="","",_xlfn.REGEXTEST(A450,"^[A-Z]{5}$"))</f>
         <v/>
       </c>
     </row>
-    <row r="451" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="451" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B451" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="452" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="452" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B452" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="453" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="453" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B453" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="454" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="454" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B454" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="455" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="455" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B455" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="456" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="456" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B456" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="457" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="457" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B457" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="458" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="458" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B458" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="459" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="459" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B459" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="460" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="460" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B460" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="461" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="461" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B461" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="462" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="462" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B462" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="463" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="463" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B463" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="464" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="464" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B464" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="465" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="465" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B465" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="466" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="466" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B466" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="467" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="467" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B467" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="468" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="468" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B468" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="469" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="469" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B469" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="470" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="470" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B470" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="471" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="471" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B471" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="472" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="472" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B472" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="473" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="473" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B473" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="474" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="474" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B474" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="475" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="475" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B475" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="476" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="476" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B476" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="477" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="477" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B477" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="478" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="478" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B478" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="479" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="479" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B479" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="480" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="480" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B480" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="481" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="481" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B481" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="482" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="482" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B482" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="483" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="483" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B483" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="484" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="484" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B484" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="485" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="485" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B485" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="486" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="486" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B486" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="487" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="487" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B487" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="488" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="488" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B488" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="489" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="489" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B489" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="490" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="490" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B490" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="491" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="491" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B491" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="492" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="492" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B492" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="493" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="493" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B493" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="494" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="494" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B494" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="495" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="495" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B495" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="496" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="496" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B496" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="497" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="497" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B497" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="498" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="498" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B498" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="499" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="499" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B499" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="500" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="500" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B500" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="501" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="501" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B501" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="502" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="502" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B502" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="503" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="503" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B503" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="504" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="504" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B504" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="505" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="505" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B505" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="506" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="506" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B506" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="507" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="507" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B507" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="508" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="508" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B508" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="509" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="509" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B509" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="510" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="510" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B510" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="511" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="511" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B511" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="512" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="512" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B512" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="513" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="513" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B513" s="2" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="514" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="514" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B514" s="2" t="str">
         <f t="shared" ref="B514:B577" si="8">IF(A514="","",_xlfn.REGEXTEST(A514,"^[A-Z]{5}$"))</f>
         <v/>
       </c>
     </row>
-    <row r="515" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="515" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B515" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="516" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="516" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B516" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="517" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="517" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B517" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="518" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="518" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B518" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="519" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="519" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B519" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="520" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="520" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B520" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="521" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="521" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B521" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="522" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="522" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B522" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="523" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="523" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B523" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="524" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="524" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B524" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="525" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="525" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B525" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="526" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="526" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B526" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="527" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="527" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B527" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="528" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="528" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B528" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="529" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="529" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B529" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="530" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="530" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B530" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="531" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="531" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B531" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="532" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="532" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B532" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="533" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="533" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B533" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="534" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="534" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B534" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="535" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="535" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B535" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="536" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="536" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B536" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="537" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="537" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B537" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="538" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="538" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B538" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="539" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="539" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B539" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="540" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="540" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B540" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="541" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="541" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B541" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="542" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="542" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B542" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="543" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="543" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B543" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="544" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="544" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B544" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="545" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="545" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B545" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="546" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="546" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B546" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="547" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="547" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B547" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="548" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="548" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B548" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="549" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="549" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B549" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="550" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="550" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B550" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="551" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="551" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B551" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="552" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="552" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B552" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="553" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="553" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B553" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="554" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="554" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B554" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="555" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="555" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B555" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="556" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="556" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B556" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="557" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="557" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B557" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="558" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="558" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B558" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="559" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="559" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B559" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="560" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="560" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B560" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="561" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="561" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B561" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="562" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="562" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B562" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="563" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="563" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B563" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="564" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="564" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B564" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="565" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="565" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B565" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="566" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="566" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B566" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="567" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="567" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B567" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="568" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="568" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B568" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="569" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="569" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B569" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="570" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="570" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B570" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="571" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="571" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B571" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="572" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="572" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B572" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="573" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="573" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B573" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="574" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="574" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B574" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="575" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="575" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B575" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="576" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="576" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B576" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="577" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="577" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B577" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="578" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="578" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B578" s="2" t="str">
         <f t="shared" ref="B578:B641" si="9">IF(A578="","",_xlfn.REGEXTEST(A578,"^[A-Z]{5}$"))</f>
         <v/>
       </c>
     </row>
-    <row r="579" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="579" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B579" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="580" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="580" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B580" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="581" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="581" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B581" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="582" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="582" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B582" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="583" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="583" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B583" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="584" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="584" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B584" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="585" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="585" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B585" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="586" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="586" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B586" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="587" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="587" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B587" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="588" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="588" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B588" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="589" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="589" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B589" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="590" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="590" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B590" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="591" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="591" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B591" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="592" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="592" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B592" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="593" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="593" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B593" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="594" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="594" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B594" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="595" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="595" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B595" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="596" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="596" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B596" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="597" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="597" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B597" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="598" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="598" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B598" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="599" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="599" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B599" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="600" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="600" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B600" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="601" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="601" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B601" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="602" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="602" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B602" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="603" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="603" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B603" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="604" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="604" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B604" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="605" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="605" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B605" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="606" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="606" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B606" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="607" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="607" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B607" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="608" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="608" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B608" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="609" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="609" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B609" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="610" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="610" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B610" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="611" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="611" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B611" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="612" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="612" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B612" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="613" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="613" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B613" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="614" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="614" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B614" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="615" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="615" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B615" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="616" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="616" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B616" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="617" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="617" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B617" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="618" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="618" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B618" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="619" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="619" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B619" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="620" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="620" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B620" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="621" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="621" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B621" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="622" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="622" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B622" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="623" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="623" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B623" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="624" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="624" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B624" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="625" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="625" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B625" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="626" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="626" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B626" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="627" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="627" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B627" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="628" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="628" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B628" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="629" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="629" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B629" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="630" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="630" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B630" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="631" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="631" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B631" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="632" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="632" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B632" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="633" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="633" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B633" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="634" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="634" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B634" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="635" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="635" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B635" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="636" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="636" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B636" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="637" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="637" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B637" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="638" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="638" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B638" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="639" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="639" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B639" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="640" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="640" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B640" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="641" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="641" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B641" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="642" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="642" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B642" s="2" t="str">
-        <f t="shared" ref="B642:B705" si="10">IF(A642="","",_xlfn.REGEXTEST(A642,"^[A-Z]{5}$"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="643" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+        <f t="shared" ref="B642:B660" si="10">IF(A642="","",_xlfn.REGEXTEST(A642,"^[A-Z]{5}$"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="643" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B643" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="644" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="644" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B644" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="645" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="645" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B645" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="646" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="646" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B646" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="647" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="647" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B647" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="648" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="648" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B648" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="649" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="649" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B649" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="650" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="650" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B650" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="651" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="651" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B651" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="652" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="652" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B652" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="653" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="653" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B653" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="654" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="654" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B654" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="655" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="655" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B655" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="656" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="656" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B656" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="657" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="657" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B657" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="658" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="658" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B658" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="659" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="659" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B659" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="660" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="660" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B660" s="2" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="661" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="661" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B661" s="2"/>
     </row>
-    <row r="662" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="662" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B662" s="2"/>
     </row>
-    <row r="663" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="663" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B663" s="2"/>
     </row>
-    <row r="664" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="664" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B664" s="2"/>
     </row>
-    <row r="665" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="665" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B665" s="2"/>
     </row>
-    <row r="666" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="666" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B666" s="2"/>
     </row>
-    <row r="667" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="667" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B667" s="2"/>
     </row>
-    <row r="668" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="668" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B668" s="2"/>
     </row>
-    <row r="669" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="669" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B669" s="2"/>
     </row>
-    <row r="670" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="670" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B670" s="2"/>
     </row>
-    <row r="671" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="671" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B671" s="2"/>
     </row>
-    <row r="672" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="672" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B672" s="2"/>
     </row>
-    <row r="673" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="673" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B673" s="2"/>
     </row>
-    <row r="674" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="674" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B674" s="2"/>
     </row>
-    <row r="675" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="675" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B675" s="2"/>
     </row>
-    <row r="676" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="676" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B676" s="2"/>
     </row>
-    <row r="677" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="677" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B677" s="2"/>
     </row>
-    <row r="678" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="678" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B678" s="2"/>
     </row>
-    <row r="679" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="679" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B679" s="2"/>
     </row>
-    <row r="680" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="680" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B680" s="2"/>
     </row>
-    <row r="681" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="681" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B681" s="2"/>
     </row>
-    <row r="682" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="682" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B682" s="2"/>
     </row>
-    <row r="683" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="683" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B683" s="2"/>
     </row>
-    <row r="684" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="684" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B684" s="2"/>
     </row>
-    <row r="685" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="685" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B685" s="2"/>
     </row>
-    <row r="686" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="686" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B686" s="2"/>
     </row>
-    <row r="687" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="687" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B687" s="2"/>
     </row>
-    <row r="688" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="688" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B688" s="2"/>
     </row>
-    <row r="689" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="689" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B689" s="2"/>
     </row>
-    <row r="690" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="690" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B690" s="2"/>
     </row>
-    <row r="691" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="691" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B691" s="2"/>
     </row>
-    <row r="692" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="692" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B692" s="2"/>
     </row>
-    <row r="693" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="693" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B693" s="2"/>
     </row>
-    <row r="694" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="694" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B694" s="2"/>
     </row>
-    <row r="695" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="695" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B695" s="2"/>
     </row>
-    <row r="696" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="696" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B696" s="2"/>
     </row>
-    <row r="697" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="697" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B697" s="2"/>
     </row>
-    <row r="698" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="698" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B698" s="2"/>
     </row>
-    <row r="699" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="699" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B699" s="2"/>
     </row>
-    <row r="700" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="700" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B700" s="2"/>
     </row>
-    <row r="701" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="701" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B701" s="2"/>
     </row>
-    <row r="702" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="702" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B702" s="2"/>
     </row>
-    <row r="703" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="703" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B703" s="2"/>
     </row>
-    <row r="704" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="704" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B704" s="2"/>
     </row>
-    <row r="705" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="705" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B705" s="2"/>
     </row>
-    <row r="706" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="706" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B706" s="2"/>
     </row>
-    <row r="707" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="707" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B707" s="2"/>
     </row>
-    <row r="708" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="708" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B708" s="2"/>
     </row>
-    <row r="709" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="709" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B709" s="2"/>
     </row>
-    <row r="710" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="710" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B710" s="2"/>
     </row>
-    <row r="711" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="711" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B711" s="2"/>
     </row>
-    <row r="712" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="712" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B712" s="2"/>
     </row>
-    <row r="713" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="713" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B713" s="2"/>
     </row>
-    <row r="714" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="714" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B714" s="2"/>
     </row>
-    <row r="715" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="715" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B715" s="2"/>
     </row>
-    <row r="716" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="716" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B716" s="2"/>
     </row>
-    <row r="717" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="717" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B717" s="2"/>
     </row>
-    <row r="718" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="718" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B718" s="2"/>
     </row>
-    <row r="719" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="719" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B719" s="2"/>
     </row>
-    <row r="720" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="720" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B720" s="2"/>
     </row>
-    <row r="721" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="721" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B721" s="2"/>
     </row>
-    <row r="722" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="722" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B722" s="2"/>
     </row>
-    <row r="723" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="723" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B723" s="2"/>
     </row>
-    <row r="724" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="724" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B724" s="2"/>
     </row>
-    <row r="725" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="725" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B725" s="2"/>
     </row>
-    <row r="726" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="726" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B726" s="2"/>
     </row>
-    <row r="727" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="727" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B727" s="2"/>
     </row>
-    <row r="728" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="728" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B728" s="2"/>
     </row>
-    <row r="729" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="729" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B729" s="2"/>
     </row>
-    <row r="730" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="730" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B730" s="2"/>
     </row>
-    <row r="731" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="731" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B731" s="2"/>
     </row>
-    <row r="732" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="732" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B732" s="2"/>
     </row>
-    <row r="733" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="733" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B733" s="2"/>
     </row>
-    <row r="734" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="734" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B734" s="2"/>
     </row>
-    <row r="735" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="735" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B735" s="2"/>
     </row>
-    <row r="736" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="736" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B736" s="2"/>
     </row>
-    <row r="737" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="737" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B737" s="2"/>
     </row>
-    <row r="738" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="738" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B738" s="2"/>
     </row>
-    <row r="739" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="739" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B739" s="2"/>
     </row>
-    <row r="740" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="740" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B740" s="2"/>
     </row>
-    <row r="741" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="741" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B741" s="2"/>
     </row>
-    <row r="742" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="742" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B742" s="2"/>
     </row>
-    <row r="743" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="743" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B743" s="2"/>
     </row>
-    <row r="744" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="744" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B744" s="2"/>
     </row>
-    <row r="745" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="745" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B745" s="2"/>
     </row>
-    <row r="746" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="746" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B746" s="2"/>
     </row>
-    <row r="747" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="747" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B747" s="2"/>
     </row>
-    <row r="748" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="748" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B748" s="2"/>
     </row>
-    <row r="749" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="749" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B749" s="2"/>
     </row>
-    <row r="750" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="750" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B750" s="2"/>
     </row>
-    <row r="751" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="751" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B751" s="2"/>
     </row>
-    <row r="752" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="752" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B752" s="2"/>
     </row>
-    <row r="753" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="753" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B753" s="2"/>
     </row>
-    <row r="754" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="754" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B754" s="2"/>
     </row>
-    <row r="755" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="755" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B755" s="2"/>
     </row>
-    <row r="756" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="756" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B756" s="2"/>
     </row>
-    <row r="757" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="757" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B757" s="2"/>
     </row>
-    <row r="758" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="758" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B758" s="2"/>
     </row>
-    <row r="759" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="759" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B759" s="2"/>
     </row>
-    <row r="760" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="760" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B760" s="2"/>
     </row>
-    <row r="761" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="761" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B761" s="2"/>
     </row>
-    <row r="762" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="762" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B762" s="2"/>
     </row>
-    <row r="763" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="763" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B763" s="2"/>
     </row>
-    <row r="764" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="764" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B764" s="2"/>
     </row>
-    <row r="765" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="765" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B765" s="2"/>
     </row>
-    <row r="766" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="766" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B766" s="2"/>
     </row>
-    <row r="767" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="767" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B767" s="2"/>
     </row>
-    <row r="768" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="768" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B768" s="2"/>
     </row>
-    <row r="769" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="769" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B769" s="2"/>
     </row>
-    <row r="770" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="770" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B770" s="2"/>
     </row>
-    <row r="771" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="771" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B771" s="2"/>
     </row>
-    <row r="772" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="772" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B772" s="2"/>
     </row>
-    <row r="773" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="773" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B773" s="2"/>
     </row>
-    <row r="774" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="774" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B774" s="2"/>
     </row>
-    <row r="775" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="775" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B775" s="2"/>
     </row>
-    <row r="776" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="776" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B776" s="2"/>
     </row>
-    <row r="777" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="777" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B777" s="2"/>
     </row>
-    <row r="778" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="778" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B778" s="2"/>
     </row>
-    <row r="779" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="779" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B779" s="2"/>
     </row>
-    <row r="780" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="780" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B780" s="2"/>
     </row>
-    <row r="781" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="781" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B781" s="2"/>
     </row>
-    <row r="782" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="782" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B782" s="2"/>
     </row>
-    <row r="783" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="783" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B783" s="2"/>
     </row>
-    <row r="784" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="784" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B784" s="2"/>
     </row>
-    <row r="785" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="785" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B785" s="2"/>
     </row>
-    <row r="786" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="786" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B786" s="2"/>
     </row>
-    <row r="787" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="787" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B787" s="2"/>
     </row>
-    <row r="788" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="788" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B788" s="2"/>
     </row>
-    <row r="789" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="789" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B789" s="2"/>
     </row>
-    <row r="790" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="790" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B790" s="2"/>
     </row>
-    <row r="791" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="791" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B791" s="2"/>
     </row>
-    <row r="792" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="792" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B792" s="2"/>
     </row>
-    <row r="793" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="793" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B793" s="2"/>
     </row>
-    <row r="794" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="794" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B794" s="2"/>
     </row>
-    <row r="795" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="795" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B795" s="2"/>
     </row>
-    <row r="796" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="796" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B796" s="2"/>
     </row>
-    <row r="797" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="797" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B797" s="2"/>
     </row>
-    <row r="798" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="798" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B798" s="2"/>
     </row>
-    <row r="799" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="799" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B799" s="2"/>
     </row>
-    <row r="800" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="800" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B800" s="2"/>
     </row>
-    <row r="801" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="801" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B801" s="2"/>
     </row>
-    <row r="802" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="802" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B802" s="2"/>
     </row>
-    <row r="803" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="803" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B803" s="2"/>
     </row>
-    <row r="804" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="804" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B804" s="2"/>
     </row>
-    <row r="805" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="805" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B805" s="2"/>
     </row>
-    <row r="806" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="806" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B806" s="2"/>
     </row>
-    <row r="807" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="807" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B807" s="2"/>
     </row>
-    <row r="808" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="808" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B808" s="2"/>
     </row>
-    <row r="809" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="809" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B809" s="2"/>
     </row>
-    <row r="810" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="810" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B810" s="2"/>
     </row>
-    <row r="811" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="811" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B811" s="2"/>
     </row>
-    <row r="812" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="812" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B812" s="2"/>
     </row>
-    <row r="813" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="813" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B813" s="2"/>
     </row>
-    <row r="814" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="814" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B814" s="2"/>
     </row>
-    <row r="815" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="815" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B815" s="2"/>
     </row>
-    <row r="816" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="816" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B816" s="2"/>
     </row>
-    <row r="817" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="817" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B817" s="2"/>
     </row>
-    <row r="818" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="818" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B818" s="2"/>
     </row>
-    <row r="819" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="819" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B819" s="2"/>
     </row>
-    <row r="820" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="820" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B820" s="2"/>
     </row>
-    <row r="821" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="821" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B821" s="2"/>
     </row>
-    <row r="822" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="822" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B822" s="2"/>
     </row>
-    <row r="823" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="823" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B823" s="2"/>
     </row>
-    <row r="824" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="824" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B824" s="2"/>
     </row>
-    <row r="825" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="825" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B825" s="2"/>
     </row>
-    <row r="826" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="826" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B826" s="2"/>
     </row>
-    <row r="827" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="827" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B827" s="2"/>
     </row>
-    <row r="828" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="828" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B828" s="2"/>
     </row>
-    <row r="829" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="829" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B829" s="2"/>
     </row>
-    <row r="830" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="830" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B830" s="2"/>
     </row>
-    <row r="831" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="831" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B831" s="2"/>
     </row>
-    <row r="832" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="832" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B832" s="2"/>
     </row>
-    <row r="833" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="833" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B833" s="2"/>
     </row>
-    <row r="834" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="834" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B834" s="2"/>
     </row>
-    <row r="835" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="835" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B835" s="2"/>
     </row>
-    <row r="836" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="836" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B836" s="2"/>
     </row>
-    <row r="837" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="837" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B837" s="2"/>
     </row>
-    <row r="838" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="838" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B838" s="2"/>
     </row>
-    <row r="839" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="839" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B839" s="2"/>
     </row>
-    <row r="840" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="840" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B840" s="2"/>
     </row>
-    <row r="841" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="841" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B841" s="2"/>
     </row>
-    <row r="842" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="842" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B842" s="2"/>
     </row>
-    <row r="843" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="843" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B843" s="2"/>
     </row>
-    <row r="844" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="844" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B844" s="2"/>
     </row>
-    <row r="845" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="845" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B845" s="2"/>
     </row>
-    <row r="846" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="846" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B846" s="2"/>
     </row>
-    <row r="847" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="847" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B847" s="2"/>
     </row>
-    <row r="848" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="848" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B848" s="2"/>
     </row>
-    <row r="849" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="849" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B849" s="2"/>
     </row>
-    <row r="850" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="850" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B850" s="2"/>
     </row>
-    <row r="851" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="851" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B851" s="2"/>
     </row>
-    <row r="852" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="852" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B852" s="2"/>
     </row>
-    <row r="853" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="853" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B853" s="2"/>
     </row>
-    <row r="854" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="854" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B854" s="2"/>
     </row>
-    <row r="855" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="855" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B855" s="2"/>
     </row>
-    <row r="856" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="856" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B856" s="2"/>
     </row>
-    <row r="857" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="857" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B857" s="2"/>
     </row>
-    <row r="858" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="858" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B858" s="2"/>
     </row>
-    <row r="859" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="859" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B859" s="2"/>
     </row>
-    <row r="860" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="860" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B860" s="2"/>
     </row>
-    <row r="861" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="861" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B861" s="2"/>
     </row>
-    <row r="862" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="862" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B862" s="2"/>
     </row>
-    <row r="863" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="863" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B863" s="2"/>
     </row>
-    <row r="864" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="864" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B864" s="2"/>
     </row>
-    <row r="865" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="865" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B865" s="2"/>
     </row>
-    <row r="866" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="866" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B866" s="2"/>
     </row>
-    <row r="867" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="867" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B867" s="2"/>
     </row>
-    <row r="868" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="868" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B868" s="2"/>
     </row>
-    <row r="869" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="869" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B869" s="2"/>
     </row>
-    <row r="870" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="870" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B870" s="2"/>
     </row>
-    <row r="871" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="871" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B871" s="2"/>
     </row>
-    <row r="872" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="872" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B872" s="2"/>
     </row>
-    <row r="873" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="873" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B873" s="2"/>
     </row>
-    <row r="874" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="874" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B874" s="2"/>
     </row>
-    <row r="875" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="875" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B875" s="2"/>
     </row>
-    <row r="876" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="876" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B876" s="2"/>
     </row>
-    <row r="877" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="877" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B877" s="2"/>
     </row>
-    <row r="878" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="878" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B878" s="2"/>
     </row>
-    <row r="879" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="879" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B879" s="2"/>
     </row>
-    <row r="880" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="880" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B880" s="2"/>
     </row>
-    <row r="881" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="881" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B881" s="2"/>
     </row>
-    <row r="882" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="882" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B882" s="2"/>
     </row>
-    <row r="883" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="883" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B883" s="2"/>
     </row>
-    <row r="884" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="884" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B884" s="2"/>
     </row>
-    <row r="885" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="885" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B885" s="2"/>
     </row>
-    <row r="886" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="886" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B886" s="2"/>
     </row>
-    <row r="887" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="887" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B887" s="2"/>
     </row>
-    <row r="888" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="888" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B888" s="2"/>
     </row>
-    <row r="889" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="889" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B889" s="2"/>
     </row>
-    <row r="890" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="890" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B890" s="2"/>
     </row>
-    <row r="891" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="891" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B891" s="2"/>
     </row>
-    <row r="892" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="892" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B892" s="2"/>
     </row>
-    <row r="893" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="893" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B893" s="2"/>
     </row>
-    <row r="894" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="894" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B894" s="2"/>
     </row>
-    <row r="895" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="895" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B895" s="2"/>
     </row>
-    <row r="896" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="896" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B896" s="2"/>
     </row>
-    <row r="897" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="897" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B897" s="2"/>
     </row>
-    <row r="898" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="898" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B898" s="2"/>
     </row>
-    <row r="899" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="899" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B899" s="2"/>
     </row>
-    <row r="900" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="900" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B900" s="2"/>
     </row>
-    <row r="901" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="901" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B901" s="2"/>
     </row>
-    <row r="902" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="902" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B902" s="2"/>
     </row>
-    <row r="903" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="903" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B903" s="2"/>
     </row>
-    <row r="904" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="904" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B904" s="2"/>
     </row>
-    <row r="905" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="905" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B905" s="2"/>
     </row>
-    <row r="906" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="906" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B906" s="2"/>
     </row>
-    <row r="907" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="907" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B907" s="2"/>
     </row>
-    <row r="908" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="908" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B908" s="2"/>
     </row>
-    <row r="909" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="909" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B909" s="2"/>
     </row>
-    <row r="910" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="910" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B910" s="2"/>
     </row>
-    <row r="911" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="911" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B911" s="2"/>
     </row>
-    <row r="912" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="912" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B912" s="2"/>
     </row>
-    <row r="913" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="913" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B913" s="2"/>
     </row>
-    <row r="914" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="914" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B914" s="2"/>
     </row>
-    <row r="915" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="915" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B915" s="2"/>
     </row>
-    <row r="916" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="916" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B916" s="2"/>
     </row>
-    <row r="917" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="917" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B917" s="2"/>
     </row>
-    <row r="918" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="918" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B918" s="2"/>
     </row>
-    <row r="919" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="919" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B919" s="2"/>
     </row>
-    <row r="920" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="920" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B920" s="2"/>
     </row>
-    <row r="921" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="921" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B921" s="2"/>
     </row>
-    <row r="922" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="922" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B922" s="2"/>
     </row>
-    <row r="923" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="923" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B923" s="2"/>
     </row>
-    <row r="924" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="924" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B924" s="2"/>
     </row>
-    <row r="925" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="925" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B925" s="2"/>
     </row>
-    <row r="926" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="926" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B926" s="2"/>
     </row>
-    <row r="927" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="927" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B927" s="2"/>
     </row>
-    <row r="928" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="928" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B928" s="2"/>
     </row>
-    <row r="929" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="929" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B929" s="2"/>
     </row>
-    <row r="930" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="930" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B930" s="2"/>
     </row>
-    <row r="931" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="931" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B931" s="2"/>
     </row>
-    <row r="932" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="932" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B932" s="2"/>
     </row>
-    <row r="933" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="933" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B933" s="2"/>
     </row>
-    <row r="934" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="934" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B934" s="2"/>
     </row>
-    <row r="935" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="935" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B935" s="2"/>
     </row>
-    <row r="936" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="936" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B936" s="2"/>
     </row>
-    <row r="937" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="937" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B937" s="2"/>
     </row>
-    <row r="938" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="938" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B938" s="2"/>
     </row>
-    <row r="939" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="939" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B939" s="2"/>
     </row>
-    <row r="940" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="940" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B940" s="2"/>
     </row>
-    <row r="941" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="941" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B941" s="2"/>
     </row>
-    <row r="942" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="942" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B942" s="2"/>
     </row>
-    <row r="943" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="943" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B943" s="2"/>
     </row>
-    <row r="944" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="944" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B944" s="2"/>
     </row>
-    <row r="945" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="945" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B945" s="2"/>
     </row>
-    <row r="946" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="946" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B946" s="2"/>
     </row>
-    <row r="947" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="947" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B947" s="2"/>
     </row>
-    <row r="948" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="948" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B948" s="2"/>
     </row>
-    <row r="949" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="949" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B949" s="2"/>
     </row>
-    <row r="950" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="950" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B950" s="2"/>
     </row>
-    <row r="951" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="951" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B951" s="2"/>
     </row>
-    <row r="952" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="952" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B952" s="2"/>
     </row>
-    <row r="953" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="953" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B953" s="2"/>
     </row>
-    <row r="954" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="954" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B954" s="2"/>
     </row>
-    <row r="955" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="955" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B955" s="2"/>
     </row>
-    <row r="956" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="956" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B956" s="2"/>
     </row>
-    <row r="957" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="957" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B957" s="2"/>
     </row>
-    <row r="958" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="958" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B958" s="2"/>
     </row>
-    <row r="959" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="959" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B959" s="2"/>
     </row>
-    <row r="960" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="960" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B960" s="2"/>
     </row>
-    <row r="961" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="961" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B961" s="2"/>
     </row>
-    <row r="962" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="962" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B962" s="2"/>
     </row>
-    <row r="963" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="963" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B963" s="2"/>
     </row>
-    <row r="964" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="964" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B964" s="2"/>
     </row>
-    <row r="965" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="965" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B965" s="2"/>
     </row>
-    <row r="966" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="966" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B966" s="2"/>
     </row>
-    <row r="967" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="967" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B967" s="2"/>
     </row>
-    <row r="968" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="968" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B968" s="2"/>
     </row>
-    <row r="969" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="969" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B969" s="2"/>
     </row>
-    <row r="970" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="970" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B970" s="2"/>
     </row>
-    <row r="971" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="971" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B971" s="2"/>
     </row>
-    <row r="972" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="972" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B972" s="2"/>
     </row>
-    <row r="973" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="973" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B973" s="2"/>
     </row>
-    <row r="974" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="974" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B974" s="2"/>
     </row>
-    <row r="975" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="975" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B975" s="2"/>
     </row>
-    <row r="976" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="976" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B976" s="2"/>
     </row>
-    <row r="977" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="977" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B977" s="2"/>
     </row>
-    <row r="978" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="978" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B978" s="2"/>
     </row>
-    <row r="979" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="979" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B979" s="2"/>
     </row>
-    <row r="980" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="980" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B980" s="2"/>
     </row>
-    <row r="981" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="981" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B981" s="2"/>
     </row>
-    <row r="982" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="982" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B982" s="2"/>
     </row>
-    <row r="983" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="983" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B983" s="2"/>
     </row>
-    <row r="984" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="984" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B984" s="2"/>
     </row>
-    <row r="985" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="985" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B985" s="2"/>
     </row>
-    <row r="986" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="986" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B986" s="2"/>
     </row>
-    <row r="987" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="987" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B987" s="2"/>
     </row>
-    <row r="988" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="988" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B988" s="2"/>
     </row>
-    <row r="989" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="989" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B989" s="2"/>
     </row>
-    <row r="990" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="990" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B990" s="2"/>
     </row>
-    <row r="991" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="991" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B991" s="2"/>
     </row>
-    <row r="992" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="992" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B992" s="2"/>
     </row>
-    <row r="993" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="993" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B993" s="2"/>
     </row>
-    <row r="994" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="994" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B994" s="2"/>
     </row>
-    <row r="995" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="995" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B995" s="2"/>
     </row>
-    <row r="996" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="996" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B996" s="2"/>
     </row>
-    <row r="997" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="997" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B997" s="2"/>
     </row>
-    <row r="998" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="998" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B998" s="2"/>
     </row>
-    <row r="999" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="999" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B999" s="2"/>
     </row>
-    <row r="1000" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="1000" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1000" s="2"/>
     </row>
   </sheetData>
@@ -8759,14 +8535,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>IF(Wordle!D4="","",UPPER(Wordle!D4)=MID(UPPER(Wordle!$N$2),1,1))</f>
         <v/>
@@ -8808,7 +8584,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>IF(Wordle!D5="","",UPPER(Wordle!D5)=MID(UPPER(Wordle!$N$2),1,1))</f>
         <v/>
@@ -8850,7 +8626,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>IF(Wordle!D6="","",UPPER(Wordle!D6)=MID(UPPER(Wordle!$N$2),1,1))</f>
         <v/>
@@ -8892,7 +8668,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f>IF(Wordle!D7="","",UPPER(Wordle!D7)=MID(UPPER(Wordle!$N$2),1,1))</f>
         <v/>
@@ -8934,7 +8710,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>IF(Wordle!D8="","",UPPER(Wordle!D8)=MID(UPPER(Wordle!$N$2),1,1))</f>
         <v/>
@@ -8976,7 +8752,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <f>IF(Wordle!D9="","",UPPER(Wordle!D9)=MID(UPPER(Wordle!$N$2),1,1))</f>
         <v/>
